--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-023_パスワード変更_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-023_パスワード変更_オンライン詳細設計書.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2336,6 +2336,31 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="109" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>・実装に合わせて逆反映：現在のパスワードの誤りも失敗回数に数える（5回でロック30分、ロック中は E-017）。@Transactional(noRollbackFor = BusinessException.class)
+・パスワードポリシー：英字・数字は半角のみ有効、UTF-8 で72バイト以内。リクエストの newPassword は @Size(max=128)
+・成功時はクライアントが古いトークンを破棄してログイン画面へ戻る（旧トークンはサーバー側でも ActiveUserFilter により無効）</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-023_パスワード変更_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-023_パスワード変更_オンライン詳細設計書.xlsx
@@ -287,6 +287,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -317,6 +320,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -347,6 +353,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2191,12 +2200,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>変更の途中で例外（例：save を失敗させる）</t>
+          <t>変更の途中で想定外の例外（RuntimeException。例：save を失敗させる）</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>ロールバックされ password_hash は変わらない</t>
+          <t>ロールバックされ password_hash は変わらない（BusinessException は対象外：失敗回数は確定する）</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -2213,7 +2222,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>既知課題</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -2223,12 +2232,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>200（現状は失効しない）</t>
+          <t>401 E-001（ActiveUserFilter が token の iat &lt; password_changed_at を拒否）</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>将来トークン失効を実装したら期待値を 401 に反転</t>
+          <t>トークン失効は実装済み（iat と password_changed_at は秒単位に切り捨てて比較）</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2249,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>既知課題</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -2250,12 +2259,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>200（現状はサーバー側で拒否しない）</t>
+          <t>403 E-019（PasswordChangeRequiredFilter。/api/auth/password のみ許可）</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>サーバー側強制を実装したら 403 に反転</t>
+          <t>サーバー側強制は実装済み</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4206,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>@Transactional（既定。ロールバック対象は RuntimeException。ONL-001 の login と違い noRollbackFor は付けない）</t>
+          <t>@Transactional(noRollbackFor = BusinessException.class)。現在のパスワード不一致（E-018）でも失敗回数の加算は確定させるため、ONL-001 の login と同様にロールバックしない。</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
@@ -5713,19 +5722,19 @@
   <mergeCells count="16">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="B23:F23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
